--- a/Compras/Ordem_compra/smartfixer_result_1779724577315.xlsx
+++ b/Compras/Ordem_compra/smartfixer_result_1779724577315.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ana.araujo\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ana.araujo\Documents\GitHub\MATERIAIS_CURSOS\Compras\Ordem_compra\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51C5C79F-AEFD-4C9D-8B33-24A1AB25A7E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA0F3E03-0F24-4F05-8A1E-79FC45DA8A03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20520" yWindow="-120" windowWidth="20640" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,13 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="99">
-  <si>
-    <t>pergunta</t>
-  </si>
-  <si>
-    <t>resposta</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="97">
   <si>
     <t>Qual é a situação da entrega no momento em que a ordem de compra é gerada?</t>
   </si>
@@ -693,13 +687,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B50"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B49"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="88.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -707,7 +701,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -715,7 +709,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -723,7 +717,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -731,7 +725,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -739,7 +733,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -747,7 +741,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -755,7 +749,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -763,7 +757,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -771,7 +765,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -779,7 +773,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -787,7 +781,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -795,7 +789,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -803,7 +797,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -811,7 +805,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -819,7 +813,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -827,7 +821,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>32</v>
       </c>
@@ -835,7 +829,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>34</v>
       </c>
@@ -843,7 +837,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>36</v>
       </c>
@@ -851,7 +845,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>38</v>
       </c>
@@ -859,7 +853,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>40</v>
       </c>
@@ -867,7 +861,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>42</v>
       </c>
@@ -875,7 +869,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>44</v>
       </c>
@@ -883,7 +877,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>46</v>
       </c>
@@ -891,7 +885,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>48</v>
       </c>
@@ -899,7 +893,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>50</v>
       </c>
@@ -907,7 +901,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>52</v>
       </c>
@@ -915,7 +909,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>54</v>
       </c>
@@ -923,7 +917,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>56</v>
       </c>
@@ -931,7 +925,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>58</v>
       </c>
@@ -939,7 +933,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>60</v>
       </c>
@@ -947,7 +941,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>62</v>
       </c>
@@ -955,7 +949,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>64</v>
       </c>
@@ -963,7 +957,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>66</v>
       </c>
@@ -971,7 +965,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="35" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>68</v>
       </c>
@@ -979,7 +973,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>70</v>
       </c>
@@ -987,7 +981,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>72</v>
       </c>
@@ -995,7 +989,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>74</v>
       </c>
@@ -1003,7 +997,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="39" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>76</v>
       </c>
@@ -1011,7 +1005,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="40" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>78</v>
       </c>
@@ -1019,23 +1013,23 @@
         <v>79</v>
       </c>
     </row>
-    <row r="41" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>80</v>
       </c>
       <c r="B41" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="42" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
+      <c r="B42" t="s">
         <v>82</v>
       </c>
-      <c r="B42" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>83</v>
       </c>
@@ -1043,7 +1037,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="44" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>85</v>
       </c>
@@ -1051,7 +1045,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="45" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>87</v>
       </c>
@@ -1059,7 +1053,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="46" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>89</v>
       </c>
@@ -1067,7 +1061,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="47" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>91</v>
       </c>
@@ -1075,7 +1069,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="48" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>93</v>
       </c>
@@ -1083,26 +1077,18 @@
         <v>94</v>
       </c>
     </row>
-    <row r="49" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>95</v>
       </c>
       <c r="B49" t="s">
         <v>96</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>97</v>
-      </c>
-      <c r="B50" t="s">
-        <v>98</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:B50" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:B49" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>